--- a/Master/4288r00/4288r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/4288r00/4288r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1674,70 +1674,70 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>2.135</v>
+        <v>1.243</v>
       </c>
       <c r="B62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C62" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D62" s="7" t="n">
-        <v>8.259399999999999</v>
+        <v>8.197100000000001</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>-2.0141</v>
+        <v>-4.1834</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>5.135</v>
+        <v>2.135</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>8.259600000000001</v>
+        <v>8.259399999999999</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-1.8896</v>
+        <v>-2.0141</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0131</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>3.136</v>
+        <v>5.135</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>8.3596</v>
+        <v>8.259600000000001</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>-2.2213</v>
+        <v>-1.8896</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.0112</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>6.136</v>
+        <v>3.136</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C65" s="6" t="n">
         <v>1</v>
@@ -1746,78 +1746,78 @@
         <v>8.3596</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-2.0959</v>
+        <v>-2.2213</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0118</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>1.137</v>
+        <v>6.136</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>8.443300000000001</v>
+        <v>8.3596</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>-2.5578</v>
+        <v>-2.0959</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.0095</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>4.137</v>
+        <v>1.137</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>8.4435</v>
+        <v>8.443300000000001</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-2.433</v>
+        <v>-2.5578</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0094</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>2.138</v>
+        <v>4.137</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>8.512</v>
+        <v>8.4435</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>-2.7753</v>
+        <v>-2.433</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>5.138</v>
+        <v>2.138</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C69" s="6" t="n">
         <v>1</v>
@@ -1826,109 +1826,129 @@
         <v>8.512</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-2.6507</v>
+        <v>-2.7753</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.0075</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>3.139</v>
+        <v>5.138</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C70" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>8.5694</v>
+        <v>8.512</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>-2.9892</v>
+        <v>-2.6507</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.0065</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>6.139</v>
+        <v>3.139</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C71" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>8.5695</v>
+        <v>8.5694</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-2.8642</v>
+        <v>-2.9892</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0068</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>1.14</v>
+        <v>6.139</v>
       </c>
       <c r="B72" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>8.618399999999999</v>
+        <v>8.5695</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>-3.3276</v>
+        <v>-2.8642</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>0.0056</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>4.14</v>
+        <v>1.14</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>8.618499999999999</v>
+        <v>8.618399999999999</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-3.2031</v>
+        <v>-3.3276</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>0.0056</v>
       </c>
     </row>
-    <row r="75">
-      <c r="E75" s="8" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>8.618499999999999</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>-3.2031</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0.0056</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F75" s="9" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" s="8" t="inlineStr">
+      <c r="F76" s="9" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F76" s="10" t="n">
+      <c r="F77" s="10" t="n">
         <v>2.1491</v>
       </c>
     </row>
